--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571184041</v>
+        <v>46157.93108138483</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108138483</v>
+        <v>46157.93177838567</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93177838567</v>
+        <v>46157.93402714364</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93402714364</v>
+        <v>46157.93720712999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93720712999</v>
+        <v>46158.28218792102</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28218792102</v>
+        <v>46158.29692936975</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29692936975</v>
+        <v>46158.2981786215</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2981786215</v>
+        <v>46158.33389754283</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33389754283</v>
+        <v>46158.36859599687</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36859599687</v>
+        <v>46158.3729020458</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
